--- a/Design Files/BLDC-Board-v1.0/BOM/Client BOM BLDC-Board-v1.0.xlsx
+++ b/Design Files/BLDC-Board-v1.0/BOM/Client BOM BLDC-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="331">
   <si>
     <t>#</t>
   </si>
@@ -348,9 +348,6 @@
     <t>TVS DIODE 5V 9.8V SOD923</t>
   </si>
   <si>
-    <t>TVS SURGE PROTECTOR 1-CH 3.3V</t>
-  </si>
-  <si>
     <t>TVS DIODE 28VWM 45.4VC SMB</t>
   </si>
   <si>
@@ -525,9 +522,6 @@
     <t>SOD-923.</t>
   </si>
   <si>
-    <t>SOD-123</t>
-  </si>
-  <si>
     <t>SMB_</t>
   </si>
   <si>
@@ -657,9 +651,6 @@
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
-    <t>AZ3003-01G</t>
-  </si>
-  <si>
     <t>SMBJ28A-13-F</t>
   </si>
   <si>
@@ -816,9 +807,6 @@
     <t>ON Semiconductor</t>
   </si>
   <si>
-    <t>Amazing</t>
-  </si>
-  <si>
     <t>Diodes</t>
   </si>
   <si>
@@ -1015,6 +1003,15 @@
   </si>
   <si>
     <t>Amphenol</t>
+  </si>
+  <si>
+    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>SD03</t>
+  </si>
+  <si>
+    <t>MDD</t>
   </si>
 </sst>
 </file>
@@ -1241,9 +1238,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1278,6 +1272,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1590,9 +1587,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1609,22 +1606,22 @@
         <v>94</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1643,16 +1640,16 @@
         <v>95</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J3" s="7">
         <v>4</v>
@@ -1675,54 +1672,54 @@
         <v>96</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J4" s="9">
         <v>1</v>
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19">
+    <row r="5" spans="1:11" s="23" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="18">
         <f>ROW(B5) - ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="I5" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="J5" s="26">
+      <c r="F5" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I5" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="J5" s="25">
         <v>2</v>
       </c>
-      <c r="K5" s="23" t="s">
-        <v>330</v>
+      <c r="K5" s="22" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1741,16 +1738,16 @@
         <v>98</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="J6" s="9">
         <v>2</v>
@@ -1773,16 +1770,16 @@
         <v>99</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
@@ -1805,16 +1802,16 @@
         <v>100</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J8" s="9">
         <v>6</v>
@@ -1837,16 +1834,16 @@
         <v>101</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J9" s="7">
         <v>1</v>
@@ -1869,16 +1866,16 @@
         <v>102</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -1901,16 +1898,16 @@
         <v>103</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="J11" s="7">
         <v>3</v>
@@ -1933,16 +1930,16 @@
         <v>104</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J12" s="9">
         <v>6</v>
@@ -1965,16 +1962,16 @@
         <v>105</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J13" s="7">
         <v>3</v>
@@ -1997,16 +1994,16 @@
         <v>106</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="J14" s="9">
         <v>1</v>
@@ -2029,16 +2026,16 @@
         <v>107</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J15" s="7">
         <v>6</v>
@@ -2061,23 +2058,23 @@
         <v>108</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J16" s="9">
         <v>2</v>
       </c>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="11">
         <f>ROW(B17) - ROW($B$2)</f>
@@ -2089,20 +2086,20 @@
       <c r="D17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>265</v>
+      <c r="E17" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>330</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J17" s="7">
         <v>2</v>
@@ -2122,19 +2119,19 @@
         <v>41</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J18" s="9">
         <v>1</v>
@@ -2154,19 +2151,19 @@
         <v>42</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
@@ -2186,19 +2183,19 @@
         <v>43</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J20" s="9">
         <v>4</v>
@@ -2218,19 +2215,19 @@
         <v>44</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J21" s="7">
         <v>4</v>
@@ -2250,19 +2247,19 @@
         <v>45</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J22" s="9">
         <v>4</v>
@@ -2282,19 +2279,19 @@
         <v>46</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J23" s="7">
         <v>8</v>
@@ -2314,19 +2311,19 @@
         <v>47</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J24" s="9">
         <v>4</v>
@@ -2346,19 +2343,19 @@
         <v>48</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J25" s="7">
         <v>1</v>
@@ -2378,19 +2375,19 @@
         <v>49</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J26" s="9">
         <v>2</v>
@@ -2410,19 +2407,19 @@
         <v>50</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J27" s="7">
         <v>1</v>
@@ -2442,19 +2439,19 @@
         <v>51</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J28" s="9">
         <v>1</v>
@@ -2474,19 +2471,19 @@
         <v>52</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J29" s="7">
         <v>4</v>
@@ -2506,19 +2503,19 @@
         <v>53</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J30" s="9">
         <v>1</v>
@@ -2538,19 +2535,19 @@
         <v>54</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G31" s="8">
         <v>1715721</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J31" s="7">
         <v>3</v>
@@ -2570,19 +2567,19 @@
         <v>55</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J32" s="9">
         <v>4</v>
@@ -2602,19 +2599,19 @@
         <v>56</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J33" s="7">
         <v>1</v>
@@ -2634,19 +2631,19 @@
         <v>57</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="J34" s="9">
         <v>1</v>
@@ -2666,19 +2663,19 @@
         <v>58</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J35" s="7">
         <v>3</v>
@@ -2698,19 +2695,19 @@
         <v>59</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J36" s="9">
         <v>4</v>
@@ -2730,19 +2727,19 @@
         <v>60</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J37" s="7">
         <v>4</v>
@@ -2762,19 +2759,19 @@
         <v>61</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J38" s="9">
         <v>4</v>
@@ -2794,19 +2791,19 @@
         <v>62</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J39" s="7">
         <v>2</v>
@@ -2826,57 +2823,57 @@
         <v>63</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J40" s="9">
         <v>1</v>
       </c>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19">
+    <row r="41" spans="1:11" s="23" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="17"/>
+      <c r="B41" s="18">
         <f>ROW(B41) - ROW($B$2)</f>
         <v>39</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="D41" s="26" t="s">
+      <c r="D41" s="25" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="G41" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="H41" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="I41" s="27" t="s">
-        <v>294</v>
-      </c>
-      <c r="J41" s="26">
+      <c r="E41" s="26" t="s">
+        <v>132</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="G41" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="H41" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I41" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="J41" s="25">
         <v>2</v>
       </c>
-      <c r="K41" s="23" t="s">
-        <v>330</v>
+      <c r="K41" s="22" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2892,19 +2889,19 @@
         <v>65</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="J42" s="9">
         <v>2</v>
@@ -2924,19 +2921,19 @@
         <v>66</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J43" s="7">
         <v>14</v>
@@ -2956,19 +2953,19 @@
         <v>67</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J44" s="9">
         <v>1</v>
@@ -2988,19 +2985,19 @@
         <v>68</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="J45" s="7">
         <v>1</v>
@@ -3020,19 +3017,19 @@
         <v>69</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="J46" s="9">
         <v>4</v>
@@ -3052,19 +3049,19 @@
         <v>70</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J47" s="7">
         <v>16</v>
@@ -3084,19 +3081,19 @@
         <v>71</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J48" s="9">
         <v>4</v>
@@ -3116,19 +3113,19 @@
         <v>72</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="J49" s="7">
         <v>1</v>
@@ -3148,17 +3145,17 @@
         <v>73</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J50" s="9">
         <v>2</v>
@@ -3178,19 +3175,19 @@
         <v>74</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J51" s="7">
         <v>1</v>
@@ -3210,19 +3207,19 @@
         <v>75</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="J52" s="9">
         <v>6</v>
@@ -3242,19 +3239,19 @@
         <v>76</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J53" s="7">
         <v>4</v>
@@ -3274,19 +3271,19 @@
         <v>77</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J54" s="9">
         <v>1</v>
@@ -3306,19 +3303,19 @@
         <v>78</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="J55" s="7">
         <v>12</v>
@@ -3338,19 +3335,19 @@
         <v>79</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J56" s="9">
         <v>1</v>
@@ -3370,57 +3367,57 @@
         <v>80</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="J57" s="7">
         <v>1</v>
       </c>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" spans="1:11" s="24" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="18"/>
-      <c r="B58" s="19">
+    <row r="58" spans="1:11" s="23" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="17"/>
+      <c r="B58" s="18">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="D58" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E58" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F58" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="H58" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="I58" s="22" t="s">
-        <v>294</v>
-      </c>
-      <c r="J58" s="21">
+      <c r="E58" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="H58" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="I58" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="J58" s="20">
         <v>4</v>
       </c>
-      <c r="K58" s="23" t="s">
-        <v>330</v>
+      <c r="K58" s="22" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3436,19 +3433,19 @@
         <v>82</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -3468,19 +3465,19 @@
         <v>83</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J60" s="9">
         <v>1</v>
@@ -3500,19 +3497,19 @@
         <v>84</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J61" s="7">
         <v>1</v>
@@ -3532,19 +3529,19 @@
         <v>85</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J62" s="9">
         <v>1</v>
@@ -3564,19 +3561,19 @@
         <v>86</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J63" s="7">
         <v>1</v>
@@ -3596,19 +3593,19 @@
         <v>87</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J64" s="9">
         <v>4</v>
@@ -3628,19 +3625,19 @@
         <v>88</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J65" s="7">
         <v>1</v>
@@ -3660,19 +3657,19 @@
         <v>89</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J66" s="9">
         <v>1</v>
@@ -3692,19 +3689,19 @@
         <v>90</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="I67" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J67" s="7">
         <v>1</v>
@@ -3724,19 +3721,19 @@
         <v>91</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="J68" s="9">
         <v>12</v>
@@ -3752,29 +3749,29 @@
       <c r="C69" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="D69" s="16" t="s">
+      <c r="D69" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="E69" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="G69" s="17" t="s">
-        <v>256</v>
-      </c>
-      <c r="H69" s="16" t="s">
+      <c r="E69" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="H69" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="I69" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="I69" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="J69" s="16">
+      <c r="J69" s="15">
         <v>1</v>
       </c>
-      <c r="K69" s="15" t="s">
-        <v>330</v>
+      <c r="K69" s="14" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3790,19 +3787,19 @@
         <v>93</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J70" s="9">
         <v>1</v>

--- a/Design Files/BLDC-Board-v1.0/BOM/Client BOM BLDC-Board-v1.0.xlsx
+++ b/Design Files/BLDC-Board-v1.0/BOM/Client BOM BLDC-Board-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="432">
   <si>
     <t>#</t>
   </si>
@@ -30,39 +30,48 @@
     <t>Capacitor</t>
   </si>
   <si>
-    <t>Electrolytic Capacitor</t>
+    <t>(TVS/ESD)</t>
   </si>
   <si>
     <t>Diode</t>
   </si>
   <si>
-    <t>ESD Protection Device</t>
+    <t>TVS Diodes</t>
   </si>
   <si>
     <t>Fuse</t>
   </si>
   <si>
+    <t>Ferrite Bead</t>
+  </si>
+  <si>
+    <t>Male Header</t>
+  </si>
+  <si>
     <t>USB Connector</t>
   </si>
   <si>
-    <t>Male Header</t>
+    <t>Terminal Blocks</t>
+  </si>
+  <si>
+    <t>Fuse Holder</t>
+  </si>
+  <si>
+    <t>Connectors (RJ45 RJ11)</t>
+  </si>
+  <si>
+    <t>Terminal Block</t>
   </si>
   <si>
     <t>Screw terminal</t>
   </si>
   <si>
-    <t>Terminal Block</t>
-  </si>
-  <si>
-    <t>Terminal Blocks</t>
+    <t>RJ45 Connector</t>
   </si>
   <si>
     <t>Relay</t>
   </si>
   <si>
-    <t>Ferrite Bead</t>
-  </si>
-  <si>
     <t>Inductor</t>
   </si>
   <si>
@@ -72,18 +81,15 @@
     <t>Transistors</t>
   </si>
   <si>
-    <t>Transistor</t>
-  </si>
-  <si>
-    <t>(BJT)</t>
-  </si>
-  <si>
     <t>Resistor</t>
   </si>
   <si>
     <t>Switch</t>
   </si>
   <si>
+    <t>DIP Switches</t>
+  </si>
+  <si>
     <t>Microcontrollers</t>
   </si>
   <si>
@@ -93,97 +99,139 @@
     <t>Optocoupler</t>
   </si>
   <si>
+    <t>Optoisolator</t>
+  </si>
+  <si>
     <t>Crystal</t>
   </si>
   <si>
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C10, C20, C21</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C4, C5</t>
-  </si>
-  <si>
-    <t>C6, C7</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>C9, C17, C35, C36, C37, C38</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>C13, C16, C18</t>
-  </si>
-  <si>
-    <t>C14, C15, C29, C30, C31, C32</t>
-  </si>
-  <si>
-    <t>C19, C33, C34</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>C23, C24, C25, C26, C27, C28</t>
-  </si>
-  <si>
-    <t>D1, D26</t>
-  </si>
-  <si>
-    <t>D2, D3</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>D6, D7, D8, D9</t>
-  </si>
-  <si>
-    <t>D10, D11, D14, D15</t>
-  </si>
-  <si>
-    <t>D12, D13, D16, D17</t>
-  </si>
-  <si>
-    <t>D18, D19, D20, D21, D22, D23, D24, D25</t>
+    <t>C1, C2, C65, C66, C67, C68, C69, C70, C71, C72</t>
+  </si>
+  <si>
+    <t>C3, C4</t>
+  </si>
+  <si>
+    <t>C5, C7, C15, C34, C35, C36, C37, C38, C39, C42, C43, C47, C48, C50, C51, C52, C53, C54, C56, C58, C59, C60, C61, C62, C63, C64</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C8, C10, C22, C23, C24, C25</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>C11, C12, C13</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C18, C19</t>
+  </si>
+  <si>
+    <t>C20, C21</t>
+  </si>
+  <si>
+    <t>C26, C27</t>
+  </si>
+  <si>
+    <t>C28, C29, C30, C31, C32, C33</t>
+  </si>
+  <si>
+    <t>C40, C41, C44, C45</t>
+  </si>
+  <si>
+    <t>C46, C49</t>
+  </si>
+  <si>
+    <t>C55</t>
+  </si>
+  <si>
+    <t>C57</t>
+  </si>
+  <si>
+    <t>C73, C74</t>
+  </si>
+  <si>
+    <t>D1, D2</t>
+  </si>
+  <si>
+    <t>D3, D4, D5, D6, D7, D8, D9, D11, D21, D22, D23, D24</t>
+  </si>
+  <si>
+    <t>D10, D12</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>D14, D15</t>
+  </si>
+  <si>
+    <t>D16, D17</t>
+  </si>
+  <si>
+    <t>D18</t>
+  </si>
+  <si>
+    <t>D19, D20</t>
+  </si>
+  <si>
+    <t>D25, D26, D27, D28</t>
   </si>
   <si>
     <t>F1, F2, F3, F4</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>J2, J4</t>
+    <t>FB1, FB2, FB3, FB4</t>
+  </si>
+  <si>
+    <t>J1, J2</t>
   </si>
   <si>
     <t>J3</t>
   </si>
   <si>
+    <t>J4</t>
+  </si>
+  <si>
     <t>J5</t>
   </si>
   <si>
-    <t>J8, J9, J13, J14</t>
-  </si>
-  <si>
-    <t>J10</t>
-  </si>
-  <si>
-    <t>J11, J12, J16</t>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>J7</t>
+  </si>
+  <si>
+    <t>J8, J9, J10, J11, J14</t>
+  </si>
+  <si>
+    <t>J12, J13</t>
+  </si>
+  <si>
+    <t>J15, J16</t>
+  </si>
+  <si>
+    <t>J17, J18, J19, J20</t>
+  </si>
+  <si>
+    <t>J21</t>
+  </si>
+  <si>
+    <t>J22, J23</t>
   </si>
   <si>
     <t>K1, K2, K3, K4</t>
@@ -195,82 +243,103 @@
     <t>L2</t>
   </si>
   <si>
-    <t>LED1, LED2, LED3</t>
+    <t>LED1, LED2, LED3, LED5</t>
+  </si>
+  <si>
+    <t>LED4</t>
   </si>
   <si>
     <t>Q1, Q2, Q3, Q4</t>
   </si>
   <si>
-    <t>Q5, Q7, Q9, Q11</t>
-  </si>
-  <si>
-    <t>Q6, Q8, Q10, Q12</t>
-  </si>
-  <si>
-    <t>R1, R2</t>
-  </si>
-  <si>
-    <t>R3</t>
+    <t>R1, R8, R12, R21, R22, R23, R78, R79, R80, R81, R88, R89, R90, R91, R101, R102, R116, R118, R119, R120</t>
+  </si>
+  <si>
+    <t>R2, R3</t>
   </si>
   <si>
     <t>R4, R5</t>
   </si>
   <si>
-    <t>R6, R8</t>
-  </si>
-  <si>
-    <t>R7, R57, R62, R63, R65, R70, R71, R73, R78, R79, R81, R86, R87, R94</t>
+    <t>R6, R7, R47, R48, R49, R50, R51, R52, R96, R97, R99</t>
   </si>
   <si>
     <t>R9</t>
   </si>
   <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>R11, R31, R45, R52</t>
-  </si>
-  <si>
-    <t>R12, R32, R36, R37, R46, R47, R48, R53, R59, R61, R67, R69, R75, R77, R83, R85</t>
-  </si>
-  <si>
-    <t>R13, R33, R34, R35</t>
-  </si>
-  <si>
-    <t>R14</t>
-  </si>
-  <si>
-    <t>R15, R17</t>
-  </si>
-  <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>R18, R19, R20, R21, R22, R26</t>
-  </si>
-  <si>
-    <t>R23, R24, R25, R27</t>
+    <t>R10, R11</t>
+  </si>
+  <si>
+    <t>R13, R14, R15, R16, R17, R18, R19, R20</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>R25</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>R27, R82, R83, R92, R93</t>
   </si>
   <si>
     <t>R28</t>
   </si>
   <si>
-    <t>R38, R39, R40, R41, R42, R49, R50, R51, R54, R55, R56, R58</t>
-  </si>
-  <si>
-    <t>R60</t>
-  </si>
-  <si>
-    <t>R64</t>
-  </si>
-  <si>
-    <t>R66, R68, R72, R74</t>
-  </si>
-  <si>
-    <t>R76</t>
-  </si>
-  <si>
-    <t>SW1</t>
+    <t>R29, R30</t>
+  </si>
+  <si>
+    <t>R31, R32</t>
+  </si>
+  <si>
+    <t>R33, R34, R35, R36, R41, R42, R43, R44, R45, R46, R58, R59</t>
+  </si>
+  <si>
+    <t>R37, R38, R39, R40</t>
+  </si>
+  <si>
+    <t>R53</t>
+  </si>
+  <si>
+    <t>R54, R55, R56, R57</t>
+  </si>
+  <si>
+    <t>R60, R61, R62, R63</t>
+  </si>
+  <si>
+    <t>R64, R65, R66, R67, R72, R73, R74, R75</t>
+  </si>
+  <si>
+    <t>R68, R69, R70, R71</t>
+  </si>
+  <si>
+    <t>R76, R77, R84, R85, R86, R87, R94, R95</t>
+  </si>
+  <si>
+    <t>R98</t>
+  </si>
+  <si>
+    <t>R100</t>
+  </si>
+  <si>
+    <t>R103, R104, R105, R106, R108, R109, R110, R111</t>
+  </si>
+  <si>
+    <t>R107</t>
+  </si>
+  <si>
+    <t>R112, R113</t>
+  </si>
+  <si>
+    <t>R114, R115, R117, R121</t>
+  </si>
+  <si>
+    <t>SW1, SW3</t>
+  </si>
+  <si>
+    <t>SW2</t>
   </si>
   <si>
     <t>U1</t>
@@ -282,19 +351,31 @@
     <t>U3</t>
   </si>
   <si>
-    <t>U4, U8, U12, U14</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>U6</t>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>U5, U6</t>
   </si>
   <si>
     <t>U7</t>
   </si>
   <si>
-    <t>U16, U17, U18, U19, U20, U21, U22, U23, U24, U25, U26, U27</t>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>U9, U10, U11, U12</t>
+  </si>
+  <si>
+    <t>U13, U14, U15, U16, U19, U20, U21, U22</t>
+  </si>
+  <si>
+    <t>U17, U18, U23, U24</t>
+  </si>
+  <si>
+    <t>U25</t>
+  </si>
+  <si>
+    <t>U26</t>
   </si>
   <si>
     <t>X1</t>
@@ -303,25 +384,34 @@
     <t>X2</t>
   </si>
   <si>
+    <t>X3</t>
+  </si>
+  <si>
     <t>Description</t>
   </si>
   <si>
+    <t>CAP CER 10PF 50V C0G/NP0 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 6.8PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 0.1UF 50V X7R 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 10V X5R 0402</t>
+  </si>
+  <si>
     <t>CAP CER 0.1UF 16V X7R 0402</t>
   </si>
   <si>
     <t>CAP CER 4700PF 50V C0G/NPO 0603</t>
   </si>
   <si>
-    <t>CAP CER 6.8PF 50V C0G/NPO 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 10PF 50V C0G/NP0 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 4.7UF 10V X5R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 0.1UF 50V X7R 0402</t>
+    <t>CAP ALUM 220UF 20% 50V SMD</t>
+  </si>
+  <si>
+    <t>CAP CER 10UF 50V X5R 1206</t>
   </si>
   <si>
     <t>CAP CER 0.1UF 50V X5R 0402</t>
@@ -330,13 +420,10 @@
     <t>CAP CER 47PF 50V C0G/NP0 0402</t>
   </si>
   <si>
-    <t>CAP CER 10UF 25V X5R 0603</t>
-  </si>
-  <si>
-    <t>22uF 200V 320mA@100kHz ±20% SMD,D8xL16.5mm Aluminum Electrolytic Capacitors - SMD ROHS</t>
-  </si>
-  <si>
-    <t>CAP ALUM 220UF 20% 50V SMD</t>
+    <t>CAP CER 22UF 25V X5R 0805</t>
+  </si>
+  <si>
+    <t>CAP CER 4.7UF 16V X5R 0603</t>
   </si>
   <si>
     <t>CAP CER 4700PF 50V X7R 0402</t>
@@ -345,6 +432,27 @@
     <t>CAP CER 0.1UF 100V X5R 0402</t>
   </si>
   <si>
+    <t>CAP ALUM 100UF 20% 25V SMD</t>
+  </si>
+  <si>
+    <t>CAP CER 30PF 50V C0G/NPO 0402</t>
+  </si>
+  <si>
+    <t>CAP CER 1UF 16V X5R 0402</t>
+  </si>
+  <si>
+    <t>50V 470pF ±10% 0402 Multilayer Ceramic Capacitors MLCC - SMD/SMT ROHS</t>
+  </si>
+  <si>
+    <t>CAP CER 0.022UF 16V X7R 0402</t>
+  </si>
+  <si>
+    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
+  </si>
+  <si>
+    <t>±5% Single 3.1V~3.5V 300mW 3.3V SOD-323 Zener Diodes ROHS</t>
+  </si>
+  <si>
     <t>TVS DIODE 5V 9.8V SOD923</t>
   </si>
   <si>
@@ -354,40 +462,58 @@
     <t>TVS DIODE 5VWM 6.3VC DSN0603-2</t>
   </si>
   <si>
-    <t>SMB(DO-214AA) TVS ROHS</t>
+    <t>TVS DIODE 24VWM 40VC SOT23-3</t>
+  </si>
+  <si>
+    <t>SOT-23 TVS ROHS</t>
+  </si>
+  <si>
+    <t>TVS DIODE 8VWM 13.6VC DO214AA</t>
   </si>
   <si>
     <t>DIODE GEN PURP 75V 150MA SOD323</t>
   </si>
   <si>
-    <t>±5% Single 3.1V~3.5V 300mW 3.3V SOD-323 Zener Diodes ROHS</t>
-  </si>
-  <si>
-    <t>TVS DIODE 5VWM SOD523</t>
-  </si>
-  <si>
-    <t>9V 200mA 100A 500mA 0805 Resettable Fuses ROHS</t>
+    <t>60V 100mA 40A 300mA 1812 Resettable Fuses ROHS</t>
+  </si>
+  <si>
+    <t>FERRITE BEAD 220 OHM 0603 1LN</t>
+  </si>
+  <si>
+    <t>Gold 250V 3A Straight Square Pins 2.5mm 4P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x4P Plugin,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>CONN HEADER VERT 3POS 2.54MM</t>
   </si>
   <si>
     <t>5A 1 16P Female Type-C SMD USB Connectors ROHS</t>
   </si>
   <si>
-    <t>Gold 250V 3A Straight Square Pins 2.5mm 4P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x4P Plugin,P=2.54mm Pin Headers ROHS</t>
-  </si>
-  <si>
-    <t>CONN HEADER VERT 3POS 2.54MM</t>
-  </si>
-  <si>
     <t>Gold 250V 3A Square Pins 2.5mm 8P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 2.54mm 1x8P Plugin,P=2.54mm Pin Headers ROHS</t>
   </si>
   <si>
+    <t>TERM BLK 2P SIDE ENT 5.08MM PCB</t>
+  </si>
+  <si>
+    <t>FUSE HOLDER BLADE 80V PCB</t>
+  </si>
+  <si>
+    <t>Gold 250V 3A Straight Square Pins 2.5mm 2P 260℃ 6mm -40℃~+105℃ 3mm 2.54mm Plugin Black Brass 1x2P Plugin,P=2.54mm Pin Headers ROHS</t>
+  </si>
+  <si>
+    <t>RJ45Receptacle Unshielded 1 Bend insert 260℃ Gold Phosphor Bronze Without LED -40℃~+85℃ Plugin Ethernet Connectors / Modular Connectors (RJ45 RJ11) ROHS</t>
+  </si>
+  <si>
+    <t>1x3P 18A -40℃~+105℃ 250V Black 12~30 Straight pin 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw terminal ROHS</t>
+  </si>
+  <si>
     <t>1x5P -40℃~+105℃ 15A 250V Green 14~26 Straight pin 5mm 1.5 1 5 Plugin,P=5mm Screw terminal ROHS</t>
   </si>
   <si>
-    <t>1x3P 18A -40℃~+105℃ 250V Green 14~30 Straight pin 5.08mm 2.5 1 3 Plugin,P=5.08mm Screw terminal ROHS</t>
-  </si>
-  <si>
-    <t>TERM BLK 2P SIDE ENT 5.08MM PCB</t>
+    <t>M4 Plugin PCB Welding Terminal ROHS</t>
+  </si>
+  <si>
+    <t>RJ45 RJReceptacle 1 WithLED Plugin Ethernet Connectors/Modular Connectors (RJ45 RJ11) ROHS</t>
   </si>
   <si>
     <t>24V 10A SPDT (1 Form C) Plugin,10.2x20.5mm Power Relays ROHS</t>
@@ -396,31 +522,34 @@
     <t>FERRITE BEAD 600 OHM 0402 1LN</t>
   </si>
   <si>
-    <t>2.7A 6.8uH ±20% 50mΩ SMD Power Inductors ROHS</t>
+    <t>FIXED IND 6.8UH 5A 48 MOHM SMD</t>
   </si>
   <si>
     <t>RED LED 0603 Light Emitting Diodes</t>
   </si>
   <si>
+    <t>Emerald 0603 Light Emitting Diodes (LED) ROHS</t>
+  </si>
+  <si>
     <t>TRANS NPN 65V 0.1A SOT23-3</t>
   </si>
   <si>
-    <t>45V 300mW 100@100mA,1V 500mA NPN SOT-23 Bipolar Transistors - BJT ROHS</t>
-  </si>
-  <si>
-    <t>45V 310mW 250@100mA,1V 800mA SOT-23 Bipolar (BJT) ROHS</t>
+    <t>RES 10K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 0 OHM JUMPER 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES 4.7K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES SMD 1M OHM 5% 1/16W 0402</t>
   </si>
   <si>
     <t>RES 5.1K OHM 1% 1/16W 0402</t>
   </si>
   <si>
-    <t>RES SMD 1M OHM 5% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES 0 OHM JUMPER 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES 10K OHM 1% 1/16W 0402</t>
+    <t>RES 33 OHM 1% 1/16W 0402</t>
   </si>
   <si>
     <t>RES 158K OHM 0.1% 1/16W 0402</t>
@@ -429,96 +558,135 @@
     <t>RES SMD 30.1KOHM 0.1% 1/16W 0402</t>
   </si>
   <si>
+    <t>RES 3.9K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 470 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 200 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 100K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 33K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 0 OHM JUMPER 1/16W 0402</t>
+  </si>
+  <si>
+    <t>100mW Thick Film Resistors ±100ppm/℃ ±1% 60.4Ω 0603 Chip Resistor - Surface Mount ROHS</t>
+  </si>
+  <si>
+    <t>RES 120 OHM 5% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES 22 OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
     <t>1W 40mΩ Surface Mount Current Sensing Resistors ±50ppm/℃ ±1% 1206 Current Sense Resistors/Shunt Resistors ROHS</t>
   </si>
   <si>
     <t>RES SMD 1K OHM 1% 1/5W 0402</t>
   </si>
   <si>
-    <t>RES SMD 13.7KOHM 0.1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES 33K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>100mW Thick Film Resistors ±100ppm/℃ ±1% 60.4Ω 0603 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
-    <t>RES 100K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES 4.7K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES 22 OHM 1% 1/20W 0201</t>
-  </si>
-  <si>
-    <t>RES 120 OHM 5% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES SMD 57.6 OHM 1% 1/10W 0402</t>
-  </si>
-  <si>
-    <t>RES 3.9K OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES 470 OHM 1% 1/16W 0402</t>
-  </si>
-  <si>
-    <t>RES 200 OHM 1% 1/16W 0402</t>
+    <t>RES 20K OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 240 OHM 1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES SMD 12.1KOHM 0.1% 1/16W 0402</t>
+  </si>
+  <si>
+    <t>RES 49.9 OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RES SMD 10K OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
+    <t>RESISTOR 0402 JUMPER ZERO OHM</t>
+  </si>
+  <si>
+    <t>RES  SMD 330R 100 mW 0603</t>
   </si>
   <si>
     <t>SWITCH TACTILE SPST-NO 0.05A 12V</t>
   </si>
   <si>
+    <t>3 positions SPST Black Flat Toggle, Raised Style SMD-6P,6x7.6mm DIP Switches ROHS</t>
+  </si>
+  <si>
     <t>IC MCU 32BIT 512KB FLASH 64LQFP</t>
   </si>
   <si>
+    <t>IC XPNDR 100KHZ I2C 20TSSOP</t>
+  </si>
+  <si>
     <t>IC REG BUCK ADJ 3A TSOT26</t>
   </si>
   <si>
     <t>70dB@(100Hz) 1.5A Fixed 3.3V~3.3V Positive 6V SOT-223 Linear Voltage Regulators (LDO) ROHS</t>
   </si>
   <si>
+    <t>IC TRANSCEIVER HALF 1/1 14VSON</t>
+  </si>
+  <si>
+    <t>IC TRANSCEIVER HALF 1/1 8SON</t>
+  </si>
+  <si>
+    <t>250Kbps transceiver 2/2 SOP-16 RS232 ICs ROHS</t>
+  </si>
+  <si>
     <t>IC CMOS 1 CIRCUIT SC70-5</t>
   </si>
   <si>
-    <t>IC TRANSCEIVER HALF 1/1 14VSON</t>
-  </si>
-  <si>
-    <t>250Kbps transceiver 2/2 SOP-16 RS232 ICs ROHS</t>
-  </si>
-  <si>
-    <t>IC TRANSCEIVER HALF 1/1 8SON</t>
-  </si>
-  <si>
     <t>Optoisolator Transistor Output 3750Vrms 1 Channel</t>
   </si>
   <si>
+    <t>15Mbit/s 80ns 2.7V~5.5V 20kV/us DC SO-5 Logic Output Optoisolators ROHS</t>
+  </si>
+  <si>
+    <t>2/3-PORT ETHERCAT SLAVE CTLR</t>
+  </si>
+  <si>
+    <t>IC EEPROM 256KBIT I2C 1MHZ 8SOIC</t>
+  </si>
+  <si>
     <t>32.768kHz 12.5pF ±20ppm MC-306 Crystals ROHS</t>
   </si>
   <si>
     <t>8MHz 18pF ±10ppm SMD5032-4P Crystals ROHS</t>
   </si>
   <si>
+    <t>25MHz 贴片晶振 18pF ±10ppm ±20ppm SMD3225-4P Crystals ROHS</t>
+  </si>
+  <si>
     <t>Footprint</t>
   </si>
   <si>
     <t>Cap-0402</t>
   </si>
   <si>
+    <t>cap-0402</t>
+  </si>
+  <si>
     <t>Cap-0603</t>
   </si>
   <si>
-    <t>cap-0402</t>
-  </si>
-  <si>
-    <t>VKMD1652D220MV</t>
-  </si>
-  <si>
     <t>UCD-220uF-10mmDia</t>
   </si>
   <si>
+    <t>Cap-1206</t>
+  </si>
+  <si>
+    <t>Cap-0805</t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
     <t>SOD-923.</t>
   </si>
   <si>
@@ -528,16 +696,16 @@
     <t>DSN0603-2</t>
   </si>
   <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
     <t>SMB Bi Directional</t>
   </si>
   <si>
-    <t>SOD-323</t>
-  </si>
-  <si>
-    <t>SOD-523</t>
-  </si>
-  <si>
-    <t>Fuse-0805</t>
+    <t>Fuse-1812_</t>
+  </si>
+  <si>
+    <t>IND-0603 (1608 Metric)</t>
   </si>
   <si>
     <t>HDR1X4_</t>
@@ -549,10 +717,25 @@
     <t>HDR 1x8 TH male</t>
   </si>
   <si>
+    <t>178.6165.0002</t>
+  </si>
+  <si>
+    <t>HDR1X2_</t>
+  </si>
+  <si>
+    <t>X12ADIWA3DY1027</t>
+  </si>
+  <si>
+    <t>DB128L-5.08-3P-BK-S</t>
+  </si>
+  <si>
     <t>WJ127-5.0-5P</t>
   </si>
   <si>
-    <t>WJ500V-5.08-3P</t>
+    <t>T44001</t>
+  </si>
+  <si>
+    <t>HR911105A</t>
   </si>
   <si>
     <t>HF33F/024-ZS3</t>
@@ -564,70 +747,88 @@
     <t>LED-0603</t>
   </si>
   <si>
-    <t>SOT-23</t>
-  </si>
-  <si>
     <t>Res-0402</t>
   </si>
   <si>
     <t>Res-0603</t>
   </si>
   <si>
+    <t>Res-0201</t>
+  </si>
+  <si>
     <t>Res-1206</t>
   </si>
   <si>
-    <t>Res-0201</t>
-  </si>
-  <si>
     <t>B3U-1000P</t>
   </si>
   <si>
+    <t>DSIC03LSGET</t>
+  </si>
+  <si>
     <t>LQFP-64(10x10)</t>
   </si>
   <si>
+    <t>TSSOP-20</t>
+  </si>
+  <si>
     <t>SOT-23-6</t>
   </si>
   <si>
     <t>SOT- 223</t>
   </si>
   <si>
+    <t>VSON-14(3x4.5)</t>
+  </si>
+  <si>
+    <t>SON-8-EP(3x3)</t>
+  </si>
+  <si>
+    <t>SO-Narrow-16</t>
+  </si>
+  <si>
     <t>SC-70-5</t>
   </si>
   <si>
-    <t>VSON-14(3x4.5)</t>
-  </si>
-  <si>
-    <t>SO-Narrow-16</t>
-  </si>
-  <si>
-    <t>SON-8-EP(3x3)</t>
-  </si>
-  <si>
     <t>SOP-4_2.54</t>
   </si>
   <si>
-    <t>MC-306</t>
+    <t>SO-5</t>
+  </si>
+  <si>
+    <t>QFN-64-EP(9x9)</t>
+  </si>
+  <si>
+    <t>CAT24C256WI-GT3</t>
+  </si>
+  <si>
+    <t>SMD3225-4P</t>
   </si>
   <si>
     <t>Manufacturer Part Number</t>
   </si>
   <si>
+    <t>GRM1555C1H100JA01D</t>
+  </si>
+  <si>
+    <t>CC0402CRNPO9BN6R8</t>
+  </si>
+  <si>
+    <t>C1005X7R1H104KT000F</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R6BB475</t>
+  </si>
+  <si>
     <t>CC0402JRX7R7BB104</t>
   </si>
   <si>
     <t>CC0603JRNPO9BN472</t>
   </si>
   <si>
-    <t>CC0402CRNPO9BN6R8</t>
-  </si>
-  <si>
-    <t>GRM1555C1H100JA01D</t>
-  </si>
-  <si>
-    <t>CC0402KRX5R6BB475</t>
-  </si>
-  <si>
-    <t>C1005X7R1H104KT000F</t>
+    <t>UCD1H221MNL1GS</t>
+  </si>
+  <si>
+    <t>CC1206KKX5R9BB106</t>
   </si>
   <si>
     <t>C1005X5R1H104K050BB</t>
@@ -636,10 +837,10 @@
     <t>GCM1555C1H470FA16D</t>
   </si>
   <si>
-    <t>C1608X5R1E106M080AC</t>
-  </si>
-  <si>
-    <t>UCD1H221MNL1GS</t>
+    <t>CC0805MKX5R8BB226</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R7BB475</t>
   </si>
   <si>
     <t>CC0402KRX7R9BB472</t>
@@ -648,6 +849,27 @@
     <t>GRM155R62A104KE14D</t>
   </si>
   <si>
+    <t>UWX1E101MCL1GB</t>
+  </si>
+  <si>
+    <t>CC0402GRNPO9BN300</t>
+  </si>
+  <si>
+    <t>CC0402KRX5R7BB105</t>
+  </si>
+  <si>
+    <t>GRM155R11H471KA01D</t>
+  </si>
+  <si>
+    <t>CC0402JRX7R7BB223</t>
+  </si>
+  <si>
+    <t>SD03</t>
+  </si>
+  <si>
+    <t>MM3Z3V3</t>
+  </si>
+  <si>
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
@@ -657,58 +879,67 @@
     <t>PESD5V0H1BSFYL</t>
   </si>
   <si>
-    <t>SMBJ26CA</t>
+    <t>CDSOT23-T24CAN-Q</t>
+  </si>
+  <si>
+    <t>SM712</t>
+  </si>
+  <si>
+    <t>SMBJ8.0CA</t>
   </si>
   <si>
     <t>1N4148WS-7-F</t>
   </si>
   <si>
-    <t>MM3Z3V3</t>
-  </si>
-  <si>
-    <t>ESD5B5.0ST1G</t>
-  </si>
-  <si>
-    <t>SMD0805P020TF</t>
+    <t>MF-MSMF010-2</t>
+  </si>
+  <si>
+    <t>BLM18PG221SN1D</t>
+  </si>
+  <si>
+    <t>X6511WV-04H-C60D30</t>
   </si>
   <si>
     <t>TYPE-C-31-M-12</t>
   </si>
   <si>
-    <t>X6511WV-04H-C60D30</t>
-  </si>
-  <si>
     <t>X6511WV-08H-C60D30</t>
   </si>
   <si>
+    <t>X6511WV-02H-C60D30</t>
+  </si>
+  <si>
     <t>BLM15AG601SN1D</t>
   </si>
   <si>
-    <t>LVC505040-6R8M-N</t>
+    <t>0630CDMCCDS-6R8MC</t>
   </si>
   <si>
     <t>NCD0603R3</t>
   </si>
   <si>
+    <t>NCD0603G2</t>
+  </si>
+  <si>
     <t>BC846B-7-F</t>
   </si>
   <si>
-    <t>BC817 6B 160-400</t>
-  </si>
-  <si>
-    <t>BC807-40</t>
+    <t>RC0402FR-0710KL</t>
+  </si>
+  <si>
+    <t>RC0603JR-070RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-074K7L</t>
+  </si>
+  <si>
+    <t>AF0402JR-071ML</t>
   </si>
   <si>
     <t>RC0402FR-075K1L</t>
   </si>
   <si>
-    <t>AF0402JR-071ML</t>
-  </si>
-  <si>
-    <t>RC0603JR-070RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-0710KL</t>
+    <t>RC0402FR-0733RL</t>
   </si>
   <si>
     <t>RT0402BRE07158KL</t>
@@ -717,93 +948,126 @@
     <t>RT0402BRD0730K1L</t>
   </si>
   <si>
+    <t>RC0402FR-073K9L</t>
+  </si>
+  <si>
+    <t>RC0402FR-07470RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-07200RL</t>
+  </si>
+  <si>
+    <t>RC0402FR-07100KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-0733KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>RTT0360R4FTP</t>
+  </si>
+  <si>
+    <t>RC0603JR-07120RL</t>
+  </si>
+  <si>
+    <t>RC0201FR-0722RL</t>
+  </si>
+  <si>
     <t>LR1206-21R040F4</t>
   </si>
   <si>
     <t>CRCW04021K00FKEDHP</t>
   </si>
   <si>
-    <t>AT0603BRD0713K7L</t>
-  </si>
-  <si>
-    <t>RC0402FR-0733KL</t>
-  </si>
-  <si>
-    <t>RTT0360R4FTP</t>
-  </si>
-  <si>
-    <t>RC0402FR-07100KL</t>
-  </si>
-  <si>
-    <t>RC0402FR-074K7L</t>
-  </si>
-  <si>
-    <t>RC0201FR-0722RL</t>
-  </si>
-  <si>
-    <t>RC0603JR-07120RL</t>
-  </si>
-  <si>
-    <t>ERJ-2RKF57R6X</t>
-  </si>
-  <si>
-    <t>RC0402FR-073K9L</t>
-  </si>
-  <si>
-    <t>RC0402FR-07470RL</t>
-  </si>
-  <si>
-    <t>RC0402FR-07200RL</t>
+    <t>RC0402FR-0720KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-07240RL</t>
+  </si>
+  <si>
+    <t>RT0402BRD0712K1L</t>
+  </si>
+  <si>
+    <t>RC0603FR-0749R9L</t>
+  </si>
+  <si>
+    <t>RC0201FR-0710KL</t>
+  </si>
+  <si>
+    <t>AC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>RC0603JR-07330RL</t>
   </si>
   <si>
     <t>STM32G0B1RET6</t>
   </si>
   <si>
+    <t>PCF8574APWR</t>
+  </si>
+  <si>
     <t>AP63300WU-7</t>
   </si>
   <si>
     <t>BL8071CLATR33</t>
   </si>
   <si>
+    <t>TCAN1463DMTRQ1</t>
+  </si>
+  <si>
+    <t>THVD2450DRBR</t>
+  </si>
+  <si>
+    <t>MAX3232ESE</t>
+  </si>
+  <si>
     <t>TLV9001IDCKR</t>
   </si>
   <si>
-    <t>TCAN1463DMTRQ1</t>
-  </si>
-  <si>
-    <t>MAX3232ESE</t>
-  </si>
-  <si>
-    <t>THVD2450DRBR</t>
-  </si>
-  <si>
     <t>IS181GB</t>
   </si>
   <si>
+    <t>TLP2361(TPL,E(T</t>
+  </si>
+  <si>
+    <t>LAN9253-I/R4X</t>
+  </si>
+  <si>
     <t>MC-306 32.7680K-A0:ROHS</t>
   </si>
   <si>
     <t>5TJ480000XYLBC</t>
   </si>
   <si>
+    <t>X322525MRB4SI</t>
+  </si>
+  <si>
     <t>Manufacturer</t>
   </si>
   <si>
+    <t>Murata</t>
+  </si>
+  <si>
     <t>Yageo</t>
   </si>
   <si>
-    <t>Murata</t>
-  </si>
-  <si>
     <t>TDK</t>
   </si>
   <si>
-    <t>Ymin</t>
-  </si>
-  <si>
     <t>Nichicon</t>
   </si>
   <si>
+    <t>Murata Electronics</t>
+  </si>
+  <si>
+    <t>MDD</t>
+  </si>
+  <si>
+    <t>JSMSEMI</t>
+  </si>
+  <si>
     <t>ON Semiconductor</t>
   </si>
   <si>
@@ -813,40 +1077,52 @@
     <t>Nexperia</t>
   </si>
   <si>
-    <t>MSKSEMI</t>
-  </si>
-  <si>
-    <t>JSMSEMI</t>
-  </si>
-  <si>
-    <t>RUILON</t>
+    <t>Bourns</t>
+  </si>
+  <si>
+    <t>TECH PUBLIC</t>
+  </si>
+  <si>
+    <t>Littelfuse</t>
+  </si>
+  <si>
+    <t>XKB</t>
   </si>
   <si>
     <t>Korean Hroparts Elec</t>
   </si>
   <si>
-    <t>XKB</t>
+    <t>Phoenix Contact</t>
+  </si>
+  <si>
+    <t>Littelfuse Wickmann</t>
+  </si>
+  <si>
+    <t>XKB Connection</t>
+  </si>
+  <si>
+    <t>DIBO</t>
   </si>
   <si>
     <t>Ningbo Kangnex Elec</t>
   </si>
   <si>
-    <t>Phoenix Contact</t>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>HANRUN</t>
   </si>
   <si>
     <t>HF(Xiamen Hongfa Electroacoustic)</t>
   </si>
   <si>
-    <t>Chlisin Elec</t>
+    <t>Sumida</t>
   </si>
   <si>
     <t>Foshan NationStar Optoelectronics</t>
   </si>
   <si>
-    <t>DOWO</t>
-  </si>
-  <si>
-    <t>KEXIN</t>
+    <t>YAGEO</t>
   </si>
   <si>
     <t>RALEC</t>
@@ -855,85 +1131,112 @@
     <t>Vishay Dale</t>
   </si>
   <si>
-    <t>YAGEO</t>
-  </si>
-  <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
     <t>Omron</t>
   </si>
   <si>
+    <t>DongGuan KINGTEK Industrial Co.,LTD</t>
+  </si>
+  <si>
     <t>STMicroelectronics</t>
   </si>
   <si>
+    <t>Texas Instruments</t>
+  </si>
+  <si>
     <t>BL(Shanghai Belling)</t>
   </si>
   <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
     <t>UMW</t>
   </si>
   <si>
     <t>Isocom</t>
   </si>
   <si>
+    <t>Toshiba</t>
+  </si>
+  <si>
+    <t>Microchip</t>
+  </si>
+  <si>
     <t>Seiko Epson</t>
   </si>
   <si>
     <t>JYJE</t>
   </si>
   <si>
+    <t>YXC</t>
+  </si>
+  <si>
+    <t>10pF</t>
+  </si>
+  <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
     <t>0.1uF</t>
   </si>
   <si>
     <t>4.7nF</t>
   </si>
   <si>
-    <t>DNP</t>
-  </si>
-  <si>
-    <t>10pF</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>100nF</t>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>10uF</t>
   </si>
   <si>
     <t>47pF</t>
   </si>
   <si>
-    <t>10uF</t>
-  </si>
-  <si>
     <t>22uF</t>
   </si>
   <si>
-    <t>220uF</t>
-  </si>
-  <si>
     <t>0.1uf</t>
   </si>
   <si>
+    <t>100uF</t>
+  </si>
+  <si>
+    <t>30pF</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>470pF</t>
+  </si>
+  <si>
+    <t>22nF</t>
+  </si>
+  <si>
     <t>68000-103HLF</t>
   </si>
   <si>
     <t>6.8uH</t>
   </si>
   <si>
+    <t>10K</t>
+  </si>
+  <si>
+    <t>0R</t>
+  </si>
+  <si>
+    <t>4.7K</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
     <t>5.1K</t>
   </si>
   <si>
-    <t>1M</t>
-  </si>
-  <si>
-    <t>0R</t>
-  </si>
-  <si>
-    <t>10K</t>
+    <t>33R</t>
   </si>
   <si>
     <t>158K</t>
@@ -942,83 +1245,83 @@
     <t>30.1K</t>
   </si>
   <si>
+    <t>3.9K</t>
+  </si>
+  <si>
+    <t>470R</t>
+  </si>
+  <si>
+    <t>200R</t>
+  </si>
+  <si>
+    <t>100K</t>
+  </si>
+  <si>
+    <t>33K</t>
+  </si>
+  <si>
+    <t>60.4R</t>
+  </si>
+  <si>
+    <t>120R</t>
+  </si>
+  <si>
+    <t>22R</t>
+  </si>
+  <si>
     <t>40mR</t>
   </si>
   <si>
     <t>1K</t>
   </si>
   <si>
-    <t>13.7K</t>
-  </si>
-  <si>
-    <t>33K</t>
-  </si>
-  <si>
-    <t>60.4R</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>4.7K</t>
-  </si>
-  <si>
-    <t>22R</t>
-  </si>
-  <si>
-    <t>120R</t>
-  </si>
-  <si>
-    <t>57.6R</t>
-  </si>
-  <si>
-    <t>3.9K</t>
-  </si>
-  <si>
-    <t>470R</t>
-  </si>
-  <si>
-    <t>200R</t>
+    <t>20K</t>
+  </si>
+  <si>
+    <t>240R</t>
+  </si>
+  <si>
+    <t>12.1k</t>
+  </si>
+  <si>
+    <t>49.9R</t>
+  </si>
+  <si>
+    <t>330R</t>
   </si>
   <si>
     <t>8MHz</t>
   </si>
   <si>
+    <t>25MHz</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>Custom</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>DO NOT MOUNT</t>
   </si>
   <si>
     <t>Amphenol</t>
-  </si>
-  <si>
-    <t>20A 350W 16V 4V 3.3V SOD-323 ESD and Surge Protection (TVS/ESD) ROHS</t>
-  </si>
-  <si>
-    <t>SD03</t>
-  </si>
-  <si>
-    <t>MDD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1062,7 +1365,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <strike/>
+      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1071,15 +1376,6 @@
     <font>
       <strike/>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <strike/>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1201,7 +1497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1238,40 +1534,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1563,19 +1836,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1587,9 +1860,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1600,28 +1873,28 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>196</v>
+        <v>261</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>255</v>
+        <v>341</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>323</v>
+        <v>426</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>321</v>
+        <v>425</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>324</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1634,93 +1907,93 @@
         <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>256</v>
+        <v>342</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
       <c r="J3" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K3" s="7"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B70" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B94" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>198</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="J4" s="9">
-        <v>1</v>
-      </c>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" spans="1:11" s="23" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18">
+      <c r="D4" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="J4" s="15">
+        <v>2</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
         <v>3</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="H5" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="J5" s="25">
-        <v>2</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>326</v>
-      </c>
+      <c r="D5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="J5" s="7">
+        <v>26</v>
+      </c>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -1728,29 +2001,29 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>257</v>
+        <v>343</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>291</v>
+        <v>385</v>
       </c>
       <c r="J6" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" s="9"/>
     </row>
@@ -1760,29 +2033,29 @@
         <f>ROW(B7) - ROW($B$2)</f>
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>201</v>
+        <v>266</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>292</v>
+        <v>386</v>
       </c>
       <c r="J7" s="7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K7" s="7"/>
     </row>
@@ -1796,25 +2069,25 @@
         <v>2</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>202</v>
+        <v>267</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>258</v>
+        <v>343</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>293</v>
+        <v>387</v>
       </c>
       <c r="J8" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K8" s="9"/>
     </row>
@@ -1824,29 +2097,29 @@
         <f>ROW(B9) - ROW($B$2)</f>
         <v>7</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="J9" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" s="7"/>
     </row>
@@ -1856,26 +2129,26 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>204</v>
+        <v>269</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>257</v>
+        <v>343</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>294</v>
+        <v>389</v>
       </c>
       <c r="J10" s="9">
         <v>1</v>
@@ -1892,57 +2165,57 @@
         <v>2</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>205</v>
+        <v>270</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>258</v>
+        <v>344</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>295</v>
+        <v>386</v>
       </c>
       <c r="J11" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>3</v>
+      <c r="C12" s="12" t="s">
+        <v>2</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>322</v>
+        <v>215</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>164</v>
+        <v>271</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>259</v>
+        <v>342</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>296</v>
+        <v>390</v>
       </c>
       <c r="J12" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K12" s="9"/>
     </row>
@@ -1956,25 +2229,25 @@
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>297</v>
+        <v>391</v>
       </c>
       <c r="J13" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K13" s="7"/>
     </row>
@@ -1988,25 +2261,25 @@
         <v>2</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>289</v>
+        <v>385</v>
       </c>
       <c r="J14" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="9"/>
     </row>
@@ -2020,25 +2293,25 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>161</v>
+        <v>215</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>257</v>
+        <v>343</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>298</v>
+        <v>387</v>
       </c>
       <c r="J15" s="7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K15" s="7"/>
     </row>
@@ -2048,61 +2321,61 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>4</v>
+      <c r="C16" s="13" t="s">
+        <v>2</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>261</v>
+        <v>342</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>325</v>
+        <v>392</v>
       </c>
       <c r="J16" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="11">
         <f>ROW(B17) - ROW($B$2)</f>
         <v>15</v>
       </c>
       <c r="C17" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="J17" s="7">
         <v>4</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="J17" s="7">
-        <v>2</v>
       </c>
       <c r="K17" s="7"/>
     </row>
@@ -2113,28 +2386,28 @@
         <v>16</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>325</v>
+        <v>394</v>
       </c>
       <c r="J18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" s="9"/>
     </row>
@@ -2145,60 +2418,60 @@
         <v>17</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>168</v>
+        <v>215</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>325</v>
+        <v>343</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>395</v>
       </c>
       <c r="J19" s="7">
         <v>1</v>
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>169</v>
+        <v>215</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>264</v>
+        <v>346</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>325</v>
+        <v>396</v>
       </c>
       <c r="J20" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20" s="9"/>
     </row>
@@ -2209,185 +2482,185 @@
         <v>19</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>325</v>
+        <v>343</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="J21" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>265</v>
+        <v>347</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
       <c r="J22" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
         <f>ROW(B23) - ROW($B$2)</f>
         <v>21</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>114</v>
+        <v>143</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>171</v>
+        <v>221</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>325</v>
+        <v>348</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J23" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>6</v>
+      <c r="C24" s="12" t="s">
+        <v>4</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>172</v>
+        <v>222</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>325</v>
+        <v>349</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J24" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="11">
         <f>ROW(B25) - ROW($B$2)</f>
         <v>23</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>322</v>
+        <v>145</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>325</v>
+        <v>350</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J25" s="7">
         <v>1</v>
       </c>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>173</v>
+        <v>224</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>325</v>
+        <v>351</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J26" s="9">
         <v>2</v>
@@ -2401,249 +2674,249 @@
         <v>25</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>174</v>
+        <v>225</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>325</v>
+        <v>352</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J27" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>175</v>
+        <v>225</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>325</v>
+        <v>353</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J28" s="9">
         <v>1</v>
       </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
         <v>27</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>322</v>
+        <v>149</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>325</v>
+        <v>354</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J29" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>322</v>
+        <v>221</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>177</v>
+        <v>289</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>325</v>
+        <v>350</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J30" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
         <v>29</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G31" s="8">
-        <v>1715721</v>
+        <v>151</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>290</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>325</v>
+        <v>352</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J31" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>322</v>
+        <v>228</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>178</v>
+        <v>291</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>325</v>
+        <v>342</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J32" s="9">
         <v>4</v>
       </c>
       <c r="K32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
         <f>ROW(B33) - ROW($B$2)</f>
         <v>31</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>179</v>
+        <v>229</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>220</v>
+        <v>292</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>325</v>
+        <v>355</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J33" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>300</v>
+        <v>230</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J34" s="9">
         <v>1</v>
@@ -2657,254 +2930,252 @@
         <v>33</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>180</v>
+        <v>429</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>222</v>
+        <v>293</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
       <c r="J35" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>181</v>
+        <v>231</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>223</v>
+        <v>294</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>262</v>
+        <v>355</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
       <c r="J36" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f>ROW(B37) - ROW($B$2)</f>
         <v>35</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>224</v>
+        <v>429</v>
+      </c>
+      <c r="G37" s="8">
+        <v>1715721</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>274</v>
+        <v>357</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
       <c r="J37" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>181</v>
+        <v>158</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>429</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>275</v>
+        <v>358</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
       <c r="J38" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K38" s="9"/>
     </row>
-    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f>ROW(B39) - ROW($B$2)</f>
         <v>37</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>256</v>
+        <v>355</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>301</v>
+        <v>428</v>
       </c>
       <c r="J39" s="7">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>302</v>
+        <v>359</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J40" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" s="23" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="17"/>
-      <c r="B41" s="18">
+    <row r="41" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
         <v>39</v>
       </c>
-      <c r="C41" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="F41" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="H41" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="I41" s="26" t="s">
-        <v>290</v>
-      </c>
-      <c r="J41" s="25">
+      <c r="C41" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J41" s="7">
         <v>2</v>
       </c>
-      <c r="K41" s="22" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K41" s="7"/>
+    </row>
+    <row r="42" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>183</v>
+        <v>429</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>303</v>
+        <v>361</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J42" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K42" s="9"/>
     </row>
@@ -2914,225 +3185,223 @@
         <f>ROW(B43) - ROW($B$2)</f>
         <v>41</v>
       </c>
-      <c r="C43" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="C43" s="12"/>
       <c r="D43" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>182</v>
+        <v>163</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>429</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>256</v>
+        <v>362</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>304</v>
+        <v>428</v>
       </c>
       <c r="J43" s="7">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>305</v>
+        <v>363</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J44" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" s="9"/>
     </row>
-    <row r="45" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f>ROW(B45) - ROW($B$2)</f>
         <v>43</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>182</v>
+        <v>165</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>429</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>256</v>
+        <v>364</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>306</v>
+        <v>428</v>
       </c>
       <c r="J45" s="7">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K45" s="7"/>
     </row>
-    <row r="46" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>184</v>
+        <v>240</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>307</v>
+        <v>342</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>428</v>
       </c>
       <c r="J46" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K46" s="9"/>
     </row>
-    <row r="47" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f>ROW(B47) - ROW($B$2)</f>
         <v>45</v>
       </c>
-      <c r="C47" s="13" t="s">
-        <v>19</v>
+      <c r="C47" s="12" t="s">
+        <v>17</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>182</v>
+        <v>429</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>277</v>
+        <v>365</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="J47" s="7">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K47" s="7"/>
     </row>
-    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>183</v>
+        <v>241</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>256</v>
+        <v>366</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>309</v>
+        <v>428</v>
       </c>
       <c r="J48" s="9">
         <v>4</v>
       </c>
       <c r="K48" s="9"/>
     </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f>ROW(B49) - ROW($B$2)</f>
         <v>47</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>19</v>
+      <c r="C49" s="12" t="s">
+        <v>18</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>182</v>
+        <v>241</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="I49" s="8" t="s">
-        <v>310</v>
+        <v>366</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>428</v>
       </c>
       <c r="J49" s="7">
         <v>1</v>
       </c>
       <c r="K49" s="7"/>
     </row>
-    <row r="50" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
         <f t="shared" si="0"/>
@@ -3142,55 +3411,57 @@
         <v>19</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>183</v>
+        <v>225</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="H50" s="9"/>
+        <v>300</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>350</v>
+      </c>
       <c r="I50" s="10" t="s">
-        <v>311</v>
+        <v>428</v>
       </c>
       <c r="J50" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K50" s="9"/>
     </row>
-    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f>ROW(B51) - ROW($B$2)</f>
         <v>49</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>312</v>
+        <v>400</v>
       </c>
       <c r="J51" s="7">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K51" s="7"/>
     </row>
@@ -3201,30 +3472,32 @@
         <v>50</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>238</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="J52" s="9">
-        <v>6</v>
-      </c>
-      <c r="K52" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="J52" s="15">
+        <v>2</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
@@ -3233,92 +3506,92 @@
         <v>51</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>239</v>
+        <v>302</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>314</v>
+        <v>401</v>
       </c>
       <c r="J53" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K53" s="7"/>
     </row>
-    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>183</v>
+        <v>242</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>240</v>
+        <v>303</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>315</v>
+        <v>402</v>
       </c>
       <c r="J54" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="K54" s="9"/>
     </row>
-    <row r="55" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f>ROW(B55) - ROW($B$2)</f>
         <v>53</v>
       </c>
-      <c r="C55" s="13" t="s">
-        <v>19</v>
+      <c r="C55" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>241</v>
+        <v>304</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>316</v>
+        <v>403</v>
       </c>
       <c r="J55" s="7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K55" s="7"/>
     </row>
@@ -3329,28 +3602,28 @@
         <v>54</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>146</v>
+        <v>175</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>317</v>
+        <v>404</v>
       </c>
       <c r="J56" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" s="9"/>
     </row>
@@ -3360,65 +3633,63 @@
         <f>ROW(B57) - ROW($B$2)</f>
         <v>55</v>
       </c>
-      <c r="C57" s="12" t="s">
-        <v>19</v>
+      <c r="C57" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>318</v>
+        <v>405</v>
       </c>
       <c r="J57" s="7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" spans="1:11" s="23" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="17"/>
-      <c r="B58" s="18">
+    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="C58" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E58" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="F58" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="G58" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="I58" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="J58" s="20">
-        <v>4</v>
-      </c>
-      <c r="K58" s="22" t="s">
-        <v>326</v>
-      </c>
+      <c r="C58" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I58" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="J58" s="9">
+        <v>1</v>
+      </c>
+      <c r="K58" s="9"/>
     </row>
     <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
@@ -3427,25 +3698,25 @@
         <v>57</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>256</v>
+        <v>343</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>319</v>
+        <v>407</v>
       </c>
       <c r="J59" s="7">
         <v>1</v>
@@ -3462,22 +3733,22 @@
         <v>20</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>322</v>
+        <v>242</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>186</v>
+        <v>309</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>280</v>
+        <v>343</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>325</v>
+        <v>408</v>
       </c>
       <c r="J60" s="9">
         <v>1</v>
@@ -3490,29 +3761,29 @@
         <f>ROW(B61) - ROW($B$2)</f>
         <v>59</v>
       </c>
-      <c r="C61" s="12" t="s">
-        <v>21</v>
+      <c r="C61" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="I61" s="10" t="s">
-        <v>325</v>
+        <v>343</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>409</v>
       </c>
       <c r="J61" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K61" s="7"/>
     </row>
@@ -3523,60 +3794,60 @@
         <v>60</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>246</v>
+        <v>311</v>
       </c>
       <c r="H62" s="9" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="J62" s="9">
         <v>1</v>
       </c>
       <c r="K62" s="9"/>
     </row>
-    <row r="63" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1"/>
       <c r="B63" s="11">
         <f>ROW(B63) - ROW($B$2)</f>
         <v>61</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>189</v>
+        <v>242</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="I63" s="10" t="s">
-        <v>325</v>
+        <v>343</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="J63" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="7"/>
     </row>
@@ -3587,92 +3858,90 @@
         <v>62</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>190</v>
+        <v>242</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>248</v>
+        <v>313</v>
       </c>
       <c r="H64" s="9" t="s">
-        <v>283</v>
+        <v>367</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>325</v>
+        <v>412</v>
       </c>
       <c r="J64" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K64" s="9"/>
     </row>
-    <row r="65" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="11">
         <f>ROW(B65) - ROW($B$2)</f>
         <v>63</v>
       </c>
-      <c r="C65" s="12" t="s">
-        <v>22</v>
+      <c r="C65" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="I65" s="10" t="s">
-        <v>325</v>
+        <v>343</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>401</v>
       </c>
       <c r="J65" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K65" s="7"/>
     </row>
-    <row r="66" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>250</v>
-      </c>
-      <c r="H66" s="9" t="s">
-        <v>284</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="H66" s="9"/>
       <c r="I66" s="10" t="s">
-        <v>325</v>
+        <v>413</v>
       </c>
       <c r="J66" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K66" s="9"/>
     </row>
@@ -3683,128 +3952,930 @@
         <v>65</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>193</v>
+        <v>243</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="I67" s="10" t="s">
-        <v>325</v>
+        <v>343</v>
+      </c>
+      <c r="I67" s="8" t="s">
+        <v>414</v>
       </c>
       <c r="J67" s="7">
         <v>1</v>
       </c>
       <c r="K67" s="7"/>
     </row>
-    <row r="68" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="11">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>194</v>
+        <v>244</v>
       </c>
       <c r="G68" s="10" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>285</v>
+        <v>343</v>
       </c>
       <c r="I68" s="10" t="s">
-        <v>325</v>
+        <v>415</v>
       </c>
       <c r="J68" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K68" s="9"/>
     </row>
-    <row r="69" spans="1:11" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="11">
         <f>ROW(B69) - ROW($B$2)</f>
         <v>67</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="H69" s="15" t="s">
-        <v>286</v>
-      </c>
-      <c r="I69" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="J69" s="15">
-        <v>1</v>
-      </c>
-      <c r="K69" s="14" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="G69" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="J69" s="7">
+        <v>4</v>
+      </c>
+      <c r="K69" s="7"/>
+    </row>
+    <row r="70" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="11">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="F70" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="H70" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="J70" s="9">
+        <v>8</v>
+      </c>
+      <c r="K70" s="9"/>
+    </row>
+    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="1"/>
+      <c r="B71" s="11">
+        <f>ROW(B71) - ROW($B$2)</f>
+        <v>69</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E71" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="J71" s="7">
+        <v>4</v>
+      </c>
+      <c r="K71" s="7"/>
+    </row>
+    <row r="72" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="B72" s="11">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="H72" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="J72" s="9">
+        <v>8</v>
+      </c>
+      <c r="K72" s="9"/>
+    </row>
+    <row r="73" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="B73" s="11">
+        <f>ROW(B73) - ROW($B$2)</f>
+        <v>71</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="H73" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="I73" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="J73" s="15">
+        <v>1</v>
+      </c>
+      <c r="K73" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1"/>
+      <c r="B74" s="11">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="C74" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H74" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="J74" s="9">
+        <v>1</v>
+      </c>
+      <c r="K74" s="9"/>
+    </row>
+    <row r="75" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="B75" s="11">
+        <f>ROW(B75) - ROW($B$2)</f>
+        <v>73</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="J75" s="7">
+        <v>8</v>
+      </c>
+      <c r="K75" s="7"/>
+    </row>
+    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1"/>
+      <c r="B76" s="11">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H76" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="J76" s="9">
+        <v>1</v>
+      </c>
+      <c r="K76" s="9"/>
+    </row>
+    <row r="77" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="1"/>
+      <c r="B77" s="11">
+        <f>ROW(B77) - ROW($B$2)</f>
+        <v>75</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E77" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="G77" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I77" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="J77" s="7">
+        <v>2</v>
+      </c>
+      <c r="K77" s="7"/>
+    </row>
+    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="1"/>
+      <c r="B78" s="11">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+      <c r="C78" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="J78" s="9">
+        <v>4</v>
+      </c>
+      <c r="K78" s="9"/>
+    </row>
+    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1"/>
+      <c r="B79" s="11">
+        <f>ROW(B79) - ROW($B$2)</f>
+        <v>77</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G79" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J79" s="7">
+        <v>2</v>
+      </c>
+      <c r="K79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1"/>
+      <c r="B80" s="11">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J80" s="9">
+        <v>1</v>
+      </c>
+      <c r="K80" s="9"/>
+    </row>
+    <row r="81" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1"/>
+      <c r="B81" s="11">
+        <f>ROW(B81) - ROW($B$2)</f>
+        <v>79</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E81" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="I81" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J81" s="7">
+        <v>1</v>
+      </c>
+      <c r="K81" s="7"/>
+    </row>
+    <row r="82" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1"/>
+      <c r="B82" s="11">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="C82" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D70" s="9" t="s">
+      <c r="D82" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J82" s="9">
+        <v>1</v>
+      </c>
+      <c r="K82" s="9"/>
+    </row>
+    <row r="83" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1"/>
+      <c r="B83" s="11">
+        <f>ROW(B83) - ROW($B$2)</f>
+        <v>81</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E83" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="G83" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J83" s="7">
+        <v>1</v>
+      </c>
+      <c r="K83" s="7"/>
+    </row>
+    <row r="84" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1"/>
+      <c r="B84" s="11">
+        <f t="shared" si="0"/>
+        <v>82</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J84" s="9">
+        <v>1</v>
+      </c>
+      <c r="K84" s="9"/>
+    </row>
+    <row r="85" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1"/>
+      <c r="B85" s="11">
+        <f>ROW(B85) - ROW($B$2)</f>
+        <v>83</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E85" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J85" s="7">
+        <v>2</v>
+      </c>
+      <c r="K85" s="7"/>
+    </row>
+    <row r="86" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1"/>
+      <c r="B86" s="11">
+        <f t="shared" si="0"/>
+        <v>84</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J86" s="9">
+        <v>1</v>
+      </c>
+      <c r="K86" s="9"/>
+    </row>
+    <row r="87" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1"/>
+      <c r="B87" s="11">
+        <f>ROW(B87) - ROW($B$2)</f>
+        <v>85</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J87" s="7">
+        <v>1</v>
+      </c>
+      <c r="K87" s="7"/>
+    </row>
+    <row r="88" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1"/>
+      <c r="B88" s="11">
+        <f t="shared" si="0"/>
+        <v>86</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J88" s="9">
+        <v>4</v>
+      </c>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1"/>
+      <c r="B89" s="11">
+        <f>ROW(B89) - ROW($B$2)</f>
+        <v>87</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E89" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="H89" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J89" s="7">
+        <v>8</v>
+      </c>
+      <c r="K89" s="7"/>
+    </row>
+    <row r="90" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1"/>
+      <c r="B90" s="11">
+        <f t="shared" si="0"/>
+        <v>88</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J90" s="9">
+        <v>4</v>
+      </c>
+      <c r="K90" s="9"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="B91" s="11">
+        <f>ROW(B91) - ROW($B$2)</f>
+        <v>89</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="H91" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J91" s="7">
+        <v>1</v>
+      </c>
+      <c r="K91" s="7"/>
+    </row>
+    <row r="92" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="B92" s="11">
+        <f t="shared" si="0"/>
+        <v>90</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="J92" s="9">
+        <v>1</v>
+      </c>
+      <c r="K92" s="9"/>
+    </row>
+    <row r="93" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="B93" s="11">
+        <f>ROW(B93) - ROW($B$2)</f>
+        <v>91</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E93" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="H93" s="15" t="s">
+        <v>379</v>
+      </c>
+      <c r="I93" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="J93" s="15">
+        <v>1</v>
+      </c>
+      <c r="K93" s="14" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1"/>
+      <c r="B94" s="11">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="I94" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="J94" s="9">
+        <v>1</v>
+      </c>
+      <c r="K94" s="9"/>
+    </row>
+    <row r="95" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1"/>
+      <c r="B95" s="11">
+        <f>ROW(B95) - ROW($B$2)</f>
         <v>93</v>
       </c>
-      <c r="E70" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="F70" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="H70" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>320</v>
-      </c>
-      <c r="J70" s="9">
+      <c r="C95" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="H95" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="J95" s="7">
         <v>1</v>
       </c>
-      <c r="K70" s="9"/>
+      <c r="K95" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
